--- a/output/graficos_dimensiones/comunal_d_env_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:17</t>
+    <t xml:space="preserve">2026-09-10 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:31</t>
+    <t xml:space="preserve">2026-09-12 22:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_metropolitana.xlsx
@@ -66,12 +66,12 @@
     <t xml:space="preserve">La Cisterna</t>
   </si>
   <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lo Prado</t>
   </si>
   <si>
-    <t xml:space="preserve">San Ramón</t>
-  </si>
-  <si>
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
@@ -111,18 +111,18 @@
     <t xml:space="preserve">Curacaví</t>
   </si>
   <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
     <t xml:space="preserve">Santiago</t>
   </si>
   <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Pinto</t>
-  </si>
-  <si>
     <t xml:space="preserve">Peñalolén</t>
   </si>
   <si>
@@ -150,18 +150,18 @@
     <t xml:space="preserve">Peñaflor</t>
   </si>
   <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
     <t xml:space="preserve">El Monte</t>
   </si>
   <si>
-    <t xml:space="preserve">Puente Alto</t>
+    <t xml:space="preserve">Paine</t>
   </si>
   <si>
     <t xml:space="preserve">Alhué</t>
   </si>
   <si>
-    <t xml:space="preserve">Paine</t>
-  </si>
-  <si>
     <t xml:space="preserve">La Pintana</t>
   </si>
   <si>
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:43</t>
+    <t xml:space="preserve">2026-09-24 00:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -634,7 +634,7 @@
         <v>2021</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>208.53</v>
+        <v>222.92</v>
       </c>
     </row>
     <row r="3">
@@ -651,7 +651,7 @@
         <v>2021</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>178.9</v>
+        <v>193.66</v>
       </c>
     </row>
     <row r="4">
@@ -668,7 +668,7 @@
         <v>2021</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>165.89</v>
+        <v>179.98</v>
       </c>
     </row>
     <row r="5">
@@ -685,7 +685,7 @@
         <v>2021</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>159.21</v>
+        <v>169.47</v>
       </c>
     </row>
     <row r="6">
@@ -702,7 +702,7 @@
         <v>2021</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>152.03</v>
+        <v>164.12</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>2021</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>149.91</v>
+        <v>160.79</v>
       </c>
     </row>
     <row r="8">
@@ -736,7 +736,7 @@
         <v>2021</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>143.79</v>
+        <v>154.16</v>
       </c>
     </row>
     <row r="9">
@@ -753,7 +753,7 @@
         <v>2021</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>142.2</v>
+        <v>151.86</v>
       </c>
     </row>
     <row r="10">
@@ -770,7 +770,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>131.92</v>
+        <v>141.67</v>
       </c>
     </row>
     <row r="11">
@@ -787,7 +787,7 @@
         <v>2021</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>128.14</v>
+        <v>137.32</v>
       </c>
     </row>
     <row r="12">
@@ -798,13 +798,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>13117</v>
+        <v>13131</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>127.91</v>
+        <v>137.06</v>
       </c>
     </row>
     <row r="13">
@@ -815,13 +815,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>13131</v>
+        <v>13117</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>127.37</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14">
@@ -838,7 +838,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>127.19</v>
+        <v>136.38</v>
       </c>
     </row>
     <row r="15">
@@ -855,7 +855,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>126.62</v>
+        <v>135.83</v>
       </c>
     </row>
     <row r="16">
@@ -872,7 +872,7 @@
         <v>2021</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>121.5</v>
+        <v>131.16</v>
       </c>
     </row>
     <row r="17">
@@ -889,7 +889,7 @@
         <v>2021</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>121.48</v>
+        <v>130.85</v>
       </c>
     </row>
     <row r="18">
@@ -906,7 +906,7 @@
         <v>2021</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>120.72</v>
+        <v>129.04</v>
       </c>
     </row>
     <row r="19">
@@ -923,7 +923,7 @@
         <v>2021</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>118.39</v>
+        <v>126.45</v>
       </c>
     </row>
     <row r="20">
@@ -940,7 +940,7 @@
         <v>2021</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>116.51</v>
+        <v>124.62</v>
       </c>
     </row>
     <row r="21">
@@ -957,7 +957,7 @@
         <v>2021</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>115.04</v>
+        <v>123.29</v>
       </c>
     </row>
     <row r="22">
@@ -974,7 +974,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>115</v>
+        <v>122.98</v>
       </c>
     </row>
     <row r="23">
@@ -991,7 +991,7 @@
         <v>2021</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>111.32</v>
+        <v>119.52</v>
       </c>
     </row>
     <row r="24">
@@ -1008,7 +1008,7 @@
         <v>2021</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>110.33</v>
+        <v>118.8</v>
       </c>
     </row>
     <row r="25">
@@ -1025,7 +1025,7 @@
         <v>2021</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>108.91</v>
+        <v>115.53</v>
       </c>
     </row>
     <row r="26">
@@ -1042,7 +1042,7 @@
         <v>2021</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>107.66</v>
+        <v>114.87</v>
       </c>
     </row>
     <row r="27">
@@ -1053,13 +1053,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>13101</v>
+        <v>13102</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>107.65</v>
+        <v>114.54</v>
       </c>
     </row>
     <row r="28">
@@ -1070,13 +1070,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>13102</v>
+        <v>13504</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>106.66</v>
+        <v>114.41</v>
       </c>
     </row>
     <row r="29">
@@ -1093,7 +1093,7 @@
         <v>2021</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>106.63</v>
+        <v>114.02</v>
       </c>
     </row>
     <row r="30">
@@ -1104,13 +1104,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>13504</v>
+        <v>13101</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>106.58</v>
+        <v>113.39</v>
       </c>
     </row>
     <row r="31">
@@ -1127,7 +1127,7 @@
         <v>2021</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>104.07</v>
+        <v>112.63</v>
       </c>
     </row>
     <row r="32">
@@ -1144,7 +1144,7 @@
         <v>2021</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>102.83</v>
+        <v>108.95</v>
       </c>
     </row>
     <row r="33">
@@ -1161,7 +1161,7 @@
         <v>2021</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>97.56</v>
+        <v>103.96</v>
       </c>
     </row>
     <row r="34">
@@ -1178,7 +1178,7 @@
         <v>2021</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>96.52</v>
+        <v>103.88</v>
       </c>
     </row>
     <row r="35">
@@ -1195,7 +1195,7 @@
         <v>2021</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>94.92</v>
+        <v>100.28</v>
       </c>
     </row>
     <row r="36">
@@ -1212,7 +1212,7 @@
         <v>2021</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>93.09</v>
+        <v>99.91</v>
       </c>
     </row>
     <row r="37">
@@ -1229,7 +1229,7 @@
         <v>2021</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>90.82</v>
+        <v>97.75</v>
       </c>
     </row>
     <row r="38">
@@ -1246,7 +1246,7 @@
         <v>2021</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>90.67</v>
+        <v>97.64</v>
       </c>
     </row>
     <row r="39">
@@ -1263,7 +1263,7 @@
         <v>2021</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>90.13</v>
+        <v>97.11</v>
       </c>
     </row>
     <row r="40">
@@ -1274,13 +1274,13 @@
         <v>44</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>13602</v>
+        <v>13201</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>89.22</v>
+        <v>95.57</v>
       </c>
     </row>
     <row r="41">
@@ -1291,13 +1291,13 @@
         <v>45</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>13201</v>
+        <v>13602</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>88.88</v>
+        <v>95.45</v>
       </c>
     </row>
     <row r="42">
@@ -1308,13 +1308,13 @@
         <v>46</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>13502</v>
+        <v>13404</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>88.33</v>
+        <v>94.42</v>
       </c>
     </row>
     <row r="43">
@@ -1325,13 +1325,13 @@
         <v>47</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13404</v>
+        <v>13502</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>2021</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>87.84</v>
+        <v>93.69</v>
       </c>
     </row>
     <row r="44">
@@ -1348,7 +1348,7 @@
         <v>2021</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>86.27</v>
+        <v>92.95</v>
       </c>
     </row>
     <row r="45">
@@ -1365,7 +1365,7 @@
         <v>2021</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>82.59</v>
+        <v>88.88</v>
       </c>
     </row>
     <row r="46">
@@ -1382,7 +1382,7 @@
         <v>2021</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>79.3</v>
+        <v>86.81</v>
       </c>
     </row>
     <row r="47">
@@ -1399,7 +1399,7 @@
         <v>2021</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>76.46</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="48">
@@ -1416,7 +1416,7 @@
         <v>2021</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>71.27</v>
+        <v>76.22</v>
       </c>
     </row>
     <row r="49">
@@ -1433,7 +1433,7 @@
         <v>2021</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>69.39</v>
+        <v>73.79</v>
       </c>
     </row>
     <row r="50">
@@ -1450,7 +1450,7 @@
         <v>2021</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>61.37</v>
+        <v>65.99</v>
       </c>
     </row>
     <row r="51">
@@ -1467,7 +1467,7 @@
         <v>2021</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>48.7</v>
+        <v>52.1</v>
       </c>
     </row>
     <row r="52">
@@ -1484,7 +1484,7 @@
         <v>2021</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>48.66</v>
+        <v>50.47</v>
       </c>
     </row>
     <row r="53">
@@ -1501,7 +1501,7 @@
         <v>2021</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>44.2</v>
+        <v>47.13</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:11</t>
+    <t xml:space="preserve">2026-10-02 16:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2021_metropolitana.xlsx
@@ -198,7 +198,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:29</t>
+    <t xml:space="preserve">2026-10-05 16:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
